--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T08:14:05+00:00</t>
+    <t>2025-05-27T14:36:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3772,7 +3772,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>263</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>268</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>274</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>280</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>287</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>293</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>316</v>
       </c>
@@ -15434,7 +15434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>529</v>
       </c>
@@ -25972,7 +25972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
         <v>689</v>
       </c>
@@ -26094,7 +26094,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="193" hidden="true">
+    <row r="193">
       <c r="A193" t="s" s="2">
         <v>693</v>
       </c>
@@ -26216,7 +26216,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="194" hidden="true">
+    <row r="194">
       <c r="A194" t="s" s="2">
         <v>703</v>
       </c>
@@ -27540,7 +27540,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
         <v>775</v>
       </c>
@@ -29462,7 +29462,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="221" hidden="true">
+    <row r="221">
       <c r="A221" t="s" s="2">
         <v>854</v>
       </c>
@@ -29584,12 +29584,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP221">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T12:29:55+00:00</t>
+    <t>2025-10-13T08:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T08:32:48+00:00</t>
+    <t>2025-10-21T08:19:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:19:27+00:00</t>
+    <t>2025-10-21T12:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
